--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL13"/>
+  <dimension ref="A1:AL12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,27 +633,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>45874.5</v>
+        <v>45874.25</v>
       </c>
     </row>
     <row r="3">
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -848,10 +848,10 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -897,12 +897,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>45874.5</v>
+        <v>45874.54166666666</v>
       </c>
     </row>
     <row r="5">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.98</v>
+        <v>4.9</v>
       </c>
       <c r="M10" t="n">
-        <v>3.66</v>
+        <v>4.6</v>
       </c>
       <c r="N10" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1784,10 +1784,10 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>45874.54166666666</v>
+        <v>45874.67708333334</v>
       </c>
     </row>
     <row r="11">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2076,138 +2076,6 @@
         </is>
       </c>
       <c r="AL12" s="3" t="n">
-        <v>45874.67708333334</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>45874</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Iceland Úrvalsdeild</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>ÍA</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Valur</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL13" s="3" t="n">
         <v>45874.67708333334</v>
       </c>
     </row>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="M10" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="N10" t="n">
-        <v>1.47</v>
+        <v>2.16</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1784,10 +1784,10 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.52</v>
+        <v>4.9</v>
       </c>
       <c r="M11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>1.47</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1916,10 +1916,10 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.8</v>
+        <v>1.52</v>
       </c>
       <c r="M12" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="N12" t="n">
-        <v>2.16</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>1.52</v>
       </c>
       <c r="M10" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="N10" t="n">
-        <v>2.16</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="M11" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>1.47</v>
+        <v>2.16</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1916,10 +1916,10 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.52</v>
+        <v>4.9</v>
       </c>
       <c r="M12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>1.47</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.52</v>
+        <v>4.9</v>
       </c>
       <c r="M10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>1.47</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1784,10 +1784,10 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.8</v>
+        <v>1.52</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="N11" t="n">
-        <v>2.16</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="M12" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="N12" t="n">
-        <v>1.47</v>
+        <v>2.16</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -854,10 +854,10 @@
         <v>2.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="M10" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="N10" t="n">
-        <v>1.47</v>
+        <v>2.16</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1784,10 +1784,10 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="N12" t="n">
-        <v>2.16</v>
+        <v>1.47</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="M10" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="N10" t="n">
-        <v>2.16</v>
+        <v>1.47</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1784,10 +1784,10 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.52</v>
+        <v>2.8</v>
       </c>
       <c r="M11" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>2.16</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,14 +1994,14 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.9</v>
+        <v>1.52</v>
       </c>
       <c r="M12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N12" t="n">
         <v>4.6</v>
       </c>
-      <c r="N12" t="n">
-        <v>1.47</v>
-      </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,14 +1730,14 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.9</v>
+        <v>1.52</v>
       </c>
       <c r="M10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N10" t="n">
         <v>4.6</v>
       </c>
-      <c r="N10" t="n">
-        <v>1.47</v>
-      </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
@@ -1784,10 +1784,10 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="N11" t="n">
-        <v>2.16</v>
+        <v>1.47</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1916,10 +1916,10 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.52</v>
+        <v>2.8</v>
       </c>
       <c r="M12" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>2.16</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.52</v>
+        <v>2.8</v>
       </c>
       <c r="M10" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>2.16</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1784,10 +1784,10 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.8</v>
+        <v>1.52</v>
       </c>
       <c r="M12" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="N12" t="n">
-        <v>2.16</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>1.52</v>
       </c>
       <c r="M10" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="N10" t="n">
-        <v>2.16</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1784,10 +1784,10 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="M11" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>1.47</v>
+        <v>2.16</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1916,10 +1916,10 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.52</v>
+        <v>4.9</v>
       </c>
       <c r="M12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>1.47</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1916,10 +1916,10 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.52</v>
+        <v>4.9</v>
       </c>
       <c r="M10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>1.47</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1784,7 +1784,7 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AE10" t="n">
         <v>1.8</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,14 +1994,14 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.9</v>
+        <v>1.52</v>
       </c>
       <c r="M12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N12" t="n">
         <v>4.6</v>
       </c>
-      <c r="N12" t="n">
-        <v>1.47</v>
-      </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AE12" t="n">
         <v>1.8</v>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,14 +1730,14 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.9</v>
+        <v>1.52</v>
       </c>
       <c r="M10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N10" t="n">
         <v>4.6</v>
       </c>
-      <c r="N10" t="n">
-        <v>1.47</v>
-      </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
@@ -1784,7 +1784,7 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AE10" t="n">
         <v>1.8</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="N11" t="n">
-        <v>2.16</v>
+        <v>1.47</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1916,10 +1916,10 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.52</v>
+        <v>2.8</v>
       </c>
       <c r="M12" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>2.16</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M3" t="n">
         <v>2.6</v>
       </c>
-      <c r="M3" t="n">
-        <v>2.9</v>
-      </c>
       <c r="N3" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.52</v>
+        <v>4.9</v>
       </c>
       <c r="M10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>1.47</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1784,7 +1784,7 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AE10" t="n">
         <v>1.8</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="M11" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>1.47</v>
+        <v>2.16</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1916,10 +1916,10 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.8</v>
+        <v>1.52</v>
       </c>
       <c r="M12" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="N12" t="n">
-        <v>2.16</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -806,46 +806,46 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="M3" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="N3" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Z3" t="n">
         <v>1.57</v>
@@ -854,28 +854,28 @@
         <v>2.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1520,10 +1520,10 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,14 +1730,14 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.9</v>
+        <v>1.52</v>
       </c>
       <c r="M10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N10" t="n">
         <v>4.6</v>
       </c>
-      <c r="N10" t="n">
-        <v>1.47</v>
-      </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
@@ -1784,7 +1784,7 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AE10" t="n">
         <v>1.8</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="N11" t="n">
-        <v>2.16</v>
+        <v>1.47</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1916,10 +1916,10 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.52</v>
+        <v>2.8</v>
       </c>
       <c r="M12" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>2.16</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1256,10 +1256,10 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1520,10 +1520,10 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.52</v>
+        <v>4.9</v>
       </c>
       <c r="M10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>1.47</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1784,7 +1784,7 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AE10" t="n">
         <v>1.8</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="M11" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>1.47</v>
+        <v>2.16</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1916,10 +1916,10 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.8</v>
+        <v>1.52</v>
       </c>
       <c r="M12" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="N12" t="n">
-        <v>2.16</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1256,10 +1256,10 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1388,10 +1388,10 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.8</v>
+        <v>1.52</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="N11" t="n">
-        <v>2.16</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1916,10 +1916,10 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.52</v>
+        <v>2.8</v>
       </c>
       <c r="M12" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>2.16</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1388,10 +1388,10 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,14 +1730,14 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.9</v>
+        <v>1.52</v>
       </c>
       <c r="M10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N10" t="n">
         <v>4.6</v>
       </c>
-      <c r="N10" t="n">
-        <v>1.47</v>
-      </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
@@ -1784,7 +1784,7 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AE10" t="n">
         <v>1.8</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.52</v>
+        <v>4.9</v>
       </c>
       <c r="M11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>1.47</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1916,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AE11" t="n">
         <v>1.8</v>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="M3" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>3.19</v>
+        <v>2.75</v>
       </c>
       <c r="O3" t="n">
         <v>2.05</v>
@@ -848,16 +848,16 @@
         <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AD3" t="n">
         <v>6.25</v>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1388,10 +1388,10 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.52</v>
+        <v>3.35</v>
       </c>
       <c r="M10" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>2.05</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1748,58 +1748,58 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.9</v>
+        <v>1.52</v>
       </c>
       <c r="M11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N11" t="n">
         <v>4.6</v>
       </c>
-      <c r="N11" t="n">
-        <v>1.47</v>
-      </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="N12" t="n">
-        <v>2.16</v>
+        <v>1.47</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="M10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V10" t="n">
         <v>3.9</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.9</v>
+        <v>6.43</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG10" t="n">
         <v>2.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,64 +1862,64 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.52</v>
+        <v>3.35</v>
       </c>
       <c r="M11" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T11" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="U11" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="V11" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AA11" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.85</v>
+        <v>2.38</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AF11" t="n">
         <v>1.5</v>
@@ -1928,10 +1928,10 @@
         <v>2.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.9</v>
+        <v>1.52</v>
       </c>
       <c r="M12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N12" t="n">
         <v>4.6</v>
       </c>
-      <c r="N12" t="n">
-        <v>1.47</v>
-      </c>
       <c r="O12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>2.63</v>
       </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.44</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="U12" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="V12" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="W12" t="n">
         <v>1.2</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
         <v>21</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.43</v>
+        <v>6</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AC12" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG12" t="n">
         <v>2.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL12"/>
+  <dimension ref="A1:AL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,12 +633,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>45874.25</v>
+        <v>45874.5</v>
       </c>
     </row>
     <row r="3">
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1256,10 +1256,10 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1388,10 +1388,10 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="M10" t="n">
         <v>4.6</v>
       </c>
       <c r="N10" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="O10" t="n">
         <v>2.63</v>
@@ -1751,19 +1751,19 @@
         <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="U10" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
@@ -1775,16 +1775,16 @@
         <v>1.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.43</v>
+        <v>6</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC10" t="n">
         <v>3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AE10" t="n">
         <v>1.8</v>
@@ -1799,7 +1799,7 @@
         <v>3</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1812,270 +1812,6 @@
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>45874.67708333334</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>45874</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Iceland Úrvalsdeild</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>FH</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Víkingur Reykjavík</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL11" s="3" t="n">
-        <v>45874.67708333334</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>45874</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Iceland Úrvalsdeild</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Breidablik</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>KA</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL12" s="3" t="n">
         <v>45874.67708333334</v>
       </c>
     </row>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1256,10 +1256,10 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1520,10 +1520,10 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1520,10 +1520,10 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1616,58 +1616,58 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.6</v>
+        <v>5.02</v>
       </c>
       <c r="M10" t="n">
         <v>4.6</v>
@@ -1757,10 +1757,10 @@
         <v>1.95</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="V10" t="n">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="W10" t="n">
         <v>1.22</v>
@@ -1769,13 +1769,13 @@
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z10" t="n">
         <v>1.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="AB10" t="n">
         <v>1.35</v>
@@ -1787,19 +1787,19 @@
         <v>1.9</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AF10" t="n">
         <v>1.44</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH10" t="n">
         <v>3</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1484,58 +1484,58 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1616,58 +1616,58 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -956,58 +956,58 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1484,58 +1484,58 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -956,58 +956,58 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1088,58 +1088,58 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1088,58 +1088,58 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1730,19 +1730,19 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.02</v>
+        <v>4.9</v>
       </c>
       <c r="M10" t="n">
         <v>4.6</v>
       </c>
       <c r="N10" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="O10" t="n">
         <v>2.63</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Q10" t="n">
         <v>1.44</v>
@@ -1763,7 +1763,7 @@
         <v>3.8</v>
       </c>
       <c r="W10" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
@@ -1775,31 +1775,31 @@
         <v>1.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC10" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AH10" t="n">
         <v>3</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1748,28 +1748,28 @@
         <v>1.44</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="S10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T10" t="n">
         <v>1.95</v>
       </c>
       <c r="U10" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="W10" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Z10" t="n">
         <v>1.05</v>
@@ -1790,7 +1790,7 @@
         <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG10" t="n">
         <v>2.5</v>
@@ -1799,7 +1799,7 @@
         <v>3</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="M2" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="N2" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="O2" t="n">
         <v>2.05</v>
@@ -722,10 +722,10 @@
         <v>1.91</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AD2" t="n">
         <v>6.25</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="M10" t="n">
-        <v>4.6</v>
+        <v>4.71</v>
       </c>
       <c r="N10" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="O10" t="n">
         <v>2.63</v>
@@ -1748,22 +1748,22 @@
         <v>1.44</v>
       </c>
       <c r="R10" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="V10" t="n">
-        <v>3.94</v>
+        <v>4.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
@@ -1775,7 +1775,7 @@
         <v>1.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="AB10" t="n">
         <v>1.36</v>
@@ -1784,22 +1784,22 @@
         <v>3.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AE10" t="n">
         <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG10" t="n">
         <v>2.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="M3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N3" t="n">
         <v>2.75</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.1</v>
       </c>
       <c r="O3" t="n">
         <v>2.05</v>
@@ -854,10 +854,10 @@
         <v>1.91</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AD3" t="n">
         <v>6.25</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="M10" t="n">
-        <v>4.71</v>
+        <v>4.6</v>
       </c>
       <c r="N10" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="O10" t="n">
         <v>2.63</v>
@@ -1748,28 +1748,28 @@
         <v>1.44</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
         <v>1.94</v>
       </c>
       <c r="U10" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="V10" t="n">
-        <v>4.1</v>
+        <v>3.94</v>
       </c>
       <c r="W10" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Z10" t="n">
         <v>1.05</v>
@@ -1778,19 +1778,19 @@
         <v>6.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC10" t="n">
         <v>3.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AG10" t="n">
         <v>2.5</v>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL10"/>
+  <dimension ref="A1:AL14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,7 +638,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="M2" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="O2" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="P2" t="n">
-        <v>4.7</v>
+        <v>11.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="R2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V2" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC2" t="n">
         <v>1.73</v>
       </c>
-      <c r="S2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V2" t="n">
-        <v>15</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AD2" t="n">
-        <v>6.25</v>
+        <v>2.88</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.06</v>
+        <v>1.35</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AH2" t="n">
-        <v>9</v>
+        <v>5.3</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -765,12 +765,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="AL3" s="3" t="n">
-        <v>45874.5</v>
+        <v>45874.54166666666</v>
       </c>
     </row>
     <row r="4">
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,22 +1070,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1118,16 +1118,16 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,22 +1466,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1514,16 +1514,16 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1532,10 +1532,10 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1557,27 +1557,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>1.63</v>
+        <v>2.45</v>
       </c>
       <c r="O9" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="P9" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V9" t="n">
+        <v>7</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AA9" t="n">
         <v>3.48</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V9" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>4.65</v>
-      </c>
       <c r="AB9" t="n">
-        <v>1.52</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.25</v>
+        <v>3.45</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.9</v>
+        <v>6.7</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>45874.54166666666</v>
+        <v>45874.58333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1689,130 +1689,658 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Dynamo Kyiv</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Paphos</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL10" s="3" t="n">
+        <v>45874.625</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45874</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Shkendija</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Qarabağ</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL11" s="3" t="n">
+        <v>45874.625</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45874</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Rangers</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Viktoria Plzeň</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P12" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL12" s="3" t="n">
+        <v>45874.65625</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45874</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>16:15</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>ÍA</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Valur</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="L13" t="n">
         <v>4.9</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M13" t="n">
         <v>4.6</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N13" t="n">
         <v>1.47</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O13" t="n">
         <v>2.63</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P13" t="n">
         <v>19</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q13" t="n">
         <v>1.44</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.2</v>
       </c>
-      <c r="S10" t="n">
+      <c r="X13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL13" s="3" t="n">
+        <v>45874.67708333334</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45874</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Quilmes</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T14" t="n">
         <v>4</v>
       </c>
-      <c r="T10" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V10" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL10" s="3" t="n">
-        <v>45874.67708333334</v>
+      <c r="U14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V14" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL14" s="3" t="n">
+        <v>45874.88194444445</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="M2" t="n">
         <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.53</v>
@@ -692,55 +692,55 @@
         <v>2.88</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="U2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="V2" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="W2" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH2" t="n">
-        <v>5.3</v>
+        <v>4.75</v>
       </c>
       <c r="AI2" t="n">
         <v>1.11</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.2</v>
+        <v>31</v>
       </c>
       <c r="M4" t="n">
-        <v>3.64</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>1.88</v>
+        <v>1.03</v>
       </c>
       <c r="O4" t="n">
-        <v>2.55</v>
+        <v>5.5</v>
       </c>
       <c r="P4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.55</v>
+        <v>1.14</v>
       </c>
       <c r="R4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.35</v>
+        <v>3.09</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>4.6</v>
+        <v>2.17</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.18</v>
+        <v>1.61</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.81</v>
+        <v>2.33</v>
       </c>
       <c r="M7" t="n">
-        <v>4.5</v>
+        <v>3.57</v>
       </c>
       <c r="N7" t="n">
-        <v>3.11</v>
+        <v>2.56</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,22 +1466,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>31</v>
+        <v>1.81</v>
       </c>
       <c r="M8" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="N8" t="n">
-        <v>1.03</v>
+        <v>3.11</v>
       </c>
       <c r="O8" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1514,16 +1514,16 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.09</v>
+        <v>2.05</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1532,10 +1532,10 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="O13" t="n">
         <v>2.63</v>
@@ -2144,58 +2144,58 @@
         <v>1.44</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S13" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="T13" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="U13" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="V13" t="n">
-        <v>4.1</v>
+        <v>4.55</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="Z13" t="n">
         <v>1.11</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.9</v>
+        <v>5.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.35</v>
+        <v>3.59</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
         <v>2.7</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
         <v>2.05</v>
@@ -2276,58 +2276,58 @@
         <v>2.3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="S14" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U14" t="n">
         <v>1.18</v>
       </c>
       <c r="V14" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AA14" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AD14" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AG14" t="n">
         <v>1.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -657,20 +657,20 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -747,12 +747,12 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['47']</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17', '81']</t>
         </is>
       </c>
       <c r="AL2" s="3" t="n">
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,106 +780,106 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '12', '32', '72', '77']</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -912,48 +912,48 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>31</v>
+        <v>1.81</v>
       </c>
       <c r="M4" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="N4" t="n">
-        <v>1.03</v>
+        <v>3.11</v>
       </c>
       <c r="O4" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -986,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.09</v>
+        <v>2.05</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1004,14 +1004,14 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15', '87']</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1053,20 +1053,20 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1']</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['86']</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
@@ -1176,48 +1176,48 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1250,16 +1250,16 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1268,10 +1268,10 @@
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['40', '42', '58']</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,102 +1440,102 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.81</v>
+        <v>4.1</v>
       </c>
       <c r="M8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P8" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AA8" t="n">
         <v>4.5</v>
       </c>
-      <c r="N8" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
       <c r="AB8" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4', '53']</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1704,102 +1704,102 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="M10" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.62</v>
+        <v>2.63</v>
       </c>
       <c r="P10" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.63</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.5</v>
+        <v>12.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.4</v>
+        <v>3.09</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AH10" t="n">
-        <v>6.75</v>
+        <v>5.93</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18']</t>
         </is>
       </c>
       <c r="AL10" s="3" t="n">
@@ -1836,19 +1836,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1858,81 +1858,81 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2.63</v>
       </c>
-      <c r="P11" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.53</v>
-      </c>
       <c r="R11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
         <v>1.36</v>
       </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AI11" t="n">
         <v>1.1</v>
       </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="AL11" s="3" t="n">
@@ -1977,20 +1977,20 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15', '45', '51']</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -912,22 +912,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.81</v>
+        <v>2.33</v>
       </c>
       <c r="M4" t="n">
-        <v>4.5</v>
+        <v>3.57</v>
       </c>
       <c r="N4" t="n">
-        <v>3.11</v>
+        <v>2.56</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>['15', '87']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,111 +1044,111 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="M5" t="n">
-        <v>5.2</v>
+        <v>3.95</v>
       </c>
       <c r="N5" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="O5" t="n">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>['1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>['86']</t>
+          <t>['4', '53']</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
@@ -1308,22 +1308,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.33</v>
+        <v>1.81</v>
       </c>
       <c r="M7" t="n">
-        <v>3.57</v>
+        <v>4.5</v>
       </c>
       <c r="N7" t="n">
-        <v>2.56</v>
+        <v>3.11</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15', '87']</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,25 +1440,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1466,85 +1466,85 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="M8" t="n">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="N8" t="n">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="O8" t="n">
-        <v>2.55</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1']</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>['4', '53']</t>
+          <t>['86']</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
@@ -2109,20 +2109,20 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -2199,12 +2199,12 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50', '90+3']</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '40']</t>
         </is>
       </c>
       <c r="AL13" s="3" t="n">

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL14"/>
+  <dimension ref="A1:AK14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,85 +543,80 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over25</t>
+          <t>FT_Odd_Over05</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under25</t>
+          <t>Odd_Over15</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Over05</t>
+          <t>Odd_Under15</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Under05</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over15</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under15</t>
+          <t>Odd_Over35</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over25</t>
+          <t>Odd_Under35</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under25</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over35</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under35</t>
+          <t>homeGoals</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_Yes</t>
+          <t>awayGoals</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_No</t>
+          <t>Odd_H_D</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over45</t>
+          <t>Odd_A_D</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under45</t>
+          <t>Odd_marcar_prim_H</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>homeGoals</t>
+          <t>Odd_marcar_prim_A</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>awayGoals</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -683,13 +678,13 @@
         <v>4.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="P2" t="n">
-        <v>11.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
       <c r="R2" t="n">
         <v>1.33</v>
@@ -704,58 +699,55 @@
         <v>1.46</v>
       </c>
       <c r="V2" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="Y2" t="n">
-        <v>11</v>
+        <v>1.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="AA2" t="n">
-        <v>4</v>
+        <v>2.66</v>
       </c>
       <c r="AB2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC2" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC2" t="n">
-        <v>2</v>
-      </c>
       <c r="AD2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>['47']</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>['17', '81']</t>
+        </is>
       </c>
       <c r="AG2" t="n">
-        <v>2.05</v>
+        <v>1.18</v>
       </c>
       <c r="AH2" t="n">
-        <v>4.75</v>
+        <v>2.2</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>['47']</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>['17', '81']</t>
-        </is>
-      </c>
-      <c r="AL2" s="3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AK2" s="3" t="n">
         <v>45874.5</v>
       </c>
     </row>
@@ -780,22 +772,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -806,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -845,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -862,11 +854,15 @@
       <c r="AD3" t="n">
         <v>0</v>
       </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['15', '87']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -877,17 +873,10 @@
       <c r="AI3" t="n">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>['3', '12', '32', '72', '77']</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL3" s="3" t="n">
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="3" t="n">
         <v>45874.54166666666</v>
       </c>
     </row>
@@ -912,22 +901,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -938,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.33</v>
+        <v>7.6</v>
       </c>
       <c r="M4" t="n">
-        <v>3.57</v>
+        <v>5.2</v>
       </c>
       <c r="N4" t="n">
-        <v>2.56</v>
+        <v>1.29</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -977,28 +966,32 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.88</v>
+        <v>1.48</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['1']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1007,19 +1000,12 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK4" s="3" t="n">
         <v>45874.54166666666</v>
       </c>
     </row>
@@ -1034,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1070,88 +1056,85 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.57</v>
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['3', '12', '32', '72', '77']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>['4', '53']</t>
-        </is>
-      </c>
-      <c r="AL5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="3" t="n">
         <v>45874.54166666666</v>
       </c>
     </row>
@@ -1211,79 +1194,76 @@
         <v>1.03</v>
       </c>
       <c r="O6" t="n">
+        <v>19</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['40', '42', '58']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
         <v>5.5</v>
       </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="AJ6" t="n">
         <v>1.14</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>['40', '42', '58']</t>
-        </is>
-      </c>
-      <c r="AL6" s="3" t="n">
+      <c r="AK6" s="3" t="n">
         <v>45874.54166666666</v>
       </c>
     </row>
@@ -1308,22 +1288,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1334,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.81</v>
+        <v>2.33</v>
       </c>
       <c r="M7" t="n">
-        <v>4.5</v>
+        <v>3.57</v>
       </c>
       <c r="N7" t="n">
-        <v>3.11</v>
+        <v>2.56</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1373,28 +1353,32 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1405,17 +1389,10 @@
       <c r="AI7" t="n">
         <v>0</v>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>['15', '87']</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL7" s="3" t="n">
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="3" t="n">
         <v>45874.54166666666</v>
       </c>
     </row>
@@ -1430,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,114 +1417,111 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="M8" t="n">
-        <v>5.2</v>
+        <v>3.95</v>
       </c>
       <c r="N8" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="O8" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.29</v>
+        <v>2.06</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.25</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>['4', '53']</t>
+        </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>['1']</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>['86']</t>
-        </is>
-      </c>
-      <c r="AL8" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK8" s="3" t="n">
         <v>45874.54166666666</v>
       </c>
     </row>
@@ -1598,88 +1572,85 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.73</v>
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="3" t="n">
         <v>45874.58333333334</v>
       </c>
     </row>
@@ -1704,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1722,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1730,88 +1701,85 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.83</v>
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['84']</t>
+        </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>['18']</t>
-        </is>
-      </c>
-      <c r="AL10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="3" t="n">
         <v>45874.625</v>
       </c>
     </row>
@@ -1836,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1854,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1862,88 +1830,85 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['18']</t>
+        </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>['84']</t>
-        </is>
-      </c>
-      <c r="AL11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="3" t="n">
         <v>45874.625</v>
       </c>
     </row>
@@ -1994,88 +1959,85 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.83</v>
+        <v>0</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['15', '45', '51']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>['15', '45', '51']</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="3" t="n">
         <v>45874.65625</v>
       </c>
     </row>
@@ -2135,13 +2097,13 @@
         <v>1.73</v>
       </c>
       <c r="O13" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>19</v>
+        <v>2.45</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="R13" t="n">
         <v>1.2</v>
@@ -2156,58 +2118,55 @@
         <v>1.67</v>
       </c>
       <c r="V13" t="n">
-        <v>4.55</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>5.25</v>
       </c>
       <c r="Y13" t="n">
-        <v>16</v>
+        <v>1.41</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.11</v>
+        <v>2.62</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.25</v>
+        <v>2.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.41</v>
+        <v>1.68</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.62</v>
+        <v>1.47</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.47</v>
+        <v>2.55</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['50', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['16', '40']</t>
+        </is>
       </c>
       <c r="AG13" t="n">
-        <v>2.55</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.59</v>
+        <v>1.29</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>['50', '90+3']</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>['16', '40']</t>
-        </is>
-      </c>
-      <c r="AL13" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AK13" s="3" t="n">
         <v>45874.67708333334</v>
       </c>
     </row>
@@ -2267,13 +2226,13 @@
         <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.05</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>4.7</v>
+        <v>1.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
         <v>1.75</v>
@@ -2288,58 +2247,55 @@
         <v>1.18</v>
       </c>
       <c r="V14" t="n">
-        <v>8.699999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="X14" t="n">
-        <v>1.11</v>
+        <v>2.09</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.75</v>
+        <v>3.08</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.75</v>
+        <v>1.28</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.09</v>
+        <v>6.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.08</v>
+        <v>1.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.28</v>
+        <v>2.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH14" t="n">
-        <v>15.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL14" s="3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK14" s="3" t="n">
         <v>45874.88194444445</v>
       </c>
     </row>

--- a/jogos_2025-08-05.xlsx
+++ b/jogos_2025-08-05.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,109 +772,109 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
       <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.81</v>
+        <v>4.1</v>
       </c>
       <c r="M3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O3" t="n">
         <v>4.5</v>
       </c>
-      <c r="N3" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['15', '87']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4', '53']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45874.54166666666</v>
@@ -1030,22 +1030,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['3', '12', '32', '72', '77']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1288,22 +1288,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '12', '32', '72', '77']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.1</v>
+        <v>1.81</v>
       </c>
       <c r="M8" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="N8" t="n">
-        <v>1.67</v>
+        <v>3.11</v>
       </c>
       <c r="O8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
+          <t>['15', '87']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>['4', '53']</t>
-        </is>
-      </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45874.54166666666</v>
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45874.58333333334</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1693,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1764,20 +1764,20 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['18']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45874.625</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1822,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1893,20 +1893,20 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['18']</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45874.625</v>
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45874.65625</v>
